--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.44878451031528</v>
+        <v>7.222927482926234</v>
       </c>
       <c r="D2" t="n">
-        <v>45.13486648744523</v>
+        <v>7.33441580420985</v>
       </c>
       <c r="E2" t="n">
-        <v>8.570798360701636</v>
+        <v>1.392754733614016</v>
       </c>
       <c r="F2" t="n">
-        <v>4.63015542510361</v>
+        <v>0.7524002565793367</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>56.49069871631396</v>
+        <v>9.179738541401019</v>
       </c>
       <c r="D3" t="n">
-        <v>56.42766598228619</v>
+        <v>9.169495722121505</v>
       </c>
       <c r="E3" t="n">
-        <v>8.570798360701636</v>
+        <v>1.392754733614016</v>
       </c>
       <c r="F3" t="n">
-        <v>4.63015542510361</v>
+        <v>0.7524002565793367</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.57652647619088</v>
+        <v>5.781185552381018</v>
       </c>
       <c r="D4" t="n">
-        <v>51.6906816238732</v>
+        <v>8.399735763879395</v>
       </c>
       <c r="E4" t="n">
-        <v>8.570798360701636</v>
+        <v>1.392754733614016</v>
       </c>
       <c r="F4" t="n">
-        <v>4.63015542510361</v>
+        <v>0.7524002565793367</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
